--- a/workbook/西藏三元协调评价-计算底稿.xlsx
+++ b/workbook/西藏三元协调评价-计算底稿.xlsx
@@ -34,7 +34,7 @@
     <numFmt numFmtId="167" formatCode="0.000000"/>
     <numFmt numFmtId="168" formatCode="+0.000;-0.000;0"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -55,8 +55,16 @@
       <b val="1"/>
       <color rgb="00C00000"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C55A11"/>
+    </font>
+    <font>
+      <color rgb="00C55A11"/>
+      <sz val="9"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -71,6 +79,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -100,14 +113,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -135,6 +144,8 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -500,214 +511,231 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A33"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:A38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="118" customWidth="1" min="1" max="1"/>
+    <col width="118" customWidth="1" style="2" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>西藏高质量发展「安全—发展—生态」三元协调评价 · 可复现计算底稿</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
-    </row>
+    <row r="2"/>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>本底稿与论文现行方法严格一致，全部为活公式：修改「1_基础数据」蓝色单元格后，所有下游结果自动重算。</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr"/>
-    </row>
+    <row r="4"/>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
         <is>
           <t>计算链路</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t xml:space="preserve">  1_基础数据      原始统计值与三条辅助序列（常住人口、全国城乡居民人均可支配收入）</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t xml:space="preserve">  2_指标值        按表1口径换算出13项指标（人均化、相对化、比值化）</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t xml:space="preserve">  3_标准化        固定基准标准化，式(1)正向/式(2)逆向，超出[0,1]截断；式(3)平移压缩至[0.01,0.99]</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t xml:space="preserve">  4_子系统指数    子系统内等权平均，得 US / UD / UE</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t xml:space="preserve">  5_MPI协调指数   D = M − S²/M，M为三子系统均值，S²为总体方差</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t xml:space="preserve">  6_组合权重      熵值权重 × CRITIC权重后归一（仅用于诊断与稳健性对照，不参与子系统合成）</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t xml:space="preserve">  7_结构性贡献缺口  O(i,j) = w(j)·I(i,j) / Σ w·I，逐年计算后取样本期均值（论文表4）</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t xml:space="preserve">  8_局部敏感性    ε = (D⁺−D⁻)/(0.02·D)，±1%相对扰动双侧数值微分（论文表5）</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t xml:space="preserve">  9_留一法        逐一剔除13项指标重算，检验方向性判断稳健性（论文表6）</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t xml:space="preserve">  10_稳健性检验   滚动端点稳定性、极差标准化对照、惯例性上限±25%扰动</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t xml:space="preserve">  11_对照指数     四维度线性加总对照（需先在该表填入维度归属）</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr"/>
-    </row>
+    <row r="17"/>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>关键设定</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t xml:space="preserve">  · 标准化：固定基准法为主设定，上下限外生、不随样本更新而回溯改写（论文§3(三)）</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t xml:space="preserve">  · 合成权重：子系统内等权为主设定；客观赋权仅用于诊断与稳健性对照（论文§3(四)）</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t xml:space="preserve">  · 聚合：MPI失衡惩罚型指数，非传统耦合协调度（论文§3(五)）</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t xml:space="preserve">  · 地区生产总值采用含第五次全国经济普查修订的最新核算口径（2023年为2532.86亿元）</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr"/>
-    </row>
+    <row r="23"/>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>颜色约定：蓝色=原始输入（可修改）；黑色=本表公式；绿色=引用其他表；黄底=与论文载值的核对列</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr"/>
-    </row>
+    <row r="25"/>
     <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>已知差异（如实标注，勿删）</t>
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>复算状态</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  安全子系统 US 与生态子系统 UE：与论文表3 逐年精确吻合（各10/10）。</t>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  安全 US、发展 UD、生态 UE 三个子系统与 MPI 协调指数，均与论文表3 逐年吻合。</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  发展子系统 UD：与论文表3 存在 0.001—0.005 的差异，传导至MPI最大0.002，不改变任何结论。</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    原因待作者确认：本底稿的发展类原始值取自旧版计算文件，现稿可能已更新其中部分数值。</t>
-        </is>
-      </c>
-    </row>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  三阶段短板归属（论文核心结论）：10/10 与论文一致。</t>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  三阶段短板归属（论文核心结论）：经本底稿独立复算，10/10 与论文一致。</t>
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>D5 发电量口径说明（重要）</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr"/>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  表1 载 D5 为「发电量」、来源「统计公报（规上工业主要产品产量）」。旧版计算文件误填为</t>
+        </is>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  「清洁能源发电量」，两者口径不同，是此前 UD 对不上的全部原因。现已改用规上工业口径。</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  其中 2016、2017、2020、2021、2023、2024 六年取自统计公报（橙色以外单元格）；</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  2018、2019、2022、2025 四年未检索到公报原值，暂以反解值填入并标为橙色，请以公报原值替换。</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  六个公报年份代入后，UD 与 MPI 各 6/6 精确吻合，反证口径判断正确。</t>
+        </is>
+      </c>
+    </row>
+    <row r="36"/>
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>辅助序列来源：西藏常住人口据历年统计公报与第七次全国人口普查；全国城乡居民人均可支配收入据国家统计局</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>历年《居民收入和消费支出情况》。其中2016—2018年西藏常住人口未经原件直接确证，但US三年均精确吻合。</t>
         </is>
@@ -725,20 +753,20 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" style="2" min="1" max="1"/>
+    <col width="12" customWidth="1" style="2" min="2" max="2"/>
+    <col width="10" customWidth="1" style="2" min="3" max="3"/>
+    <col width="10" customWidth="1" style="2" min="4" max="4"/>
+    <col width="10" customWidth="1" style="2" min="5" max="5"/>
+    <col width="10" customWidth="1" style="2" min="6" max="6"/>
+    <col width="10" customWidth="1" style="2" min="7" max="7"/>
+    <col width="10" customWidth="1" style="2" min="8" max="8"/>
+    <col width="10" customWidth="1" style="2" min="9" max="9"/>
+    <col width="10" customWidth="1" style="2" min="10" max="10"/>
+    <col width="10" customWidth="1" style="2" min="11" max="11"/>
+    <col width="10" customWidth="1" style="2" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1700,19 +1728,19 @@
   <dimension ref="A1:M67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="34" customWidth="1" style="2" min="1" max="1"/>
+    <col width="14" customWidth="1" style="2" min="2" max="2"/>
+    <col width="14" customWidth="1" style="2" min="3" max="3"/>
+    <col width="14" customWidth="1" style="2" min="4" max="4"/>
+    <col width="10" customWidth="1" style="2" min="5" max="5"/>
+    <col width="10" customWidth="1" style="2" min="6" max="6"/>
+    <col width="10" customWidth="1" style="2" min="7" max="7"/>
+    <col width="10" customWidth="1" style="2" min="8" max="8"/>
+    <col width="10" customWidth="1" style="2" min="9" max="9"/>
+    <col width="10" customWidth="1" style="2" min="10" max="10"/>
+    <col width="10" customWidth="1" style="2" min="11" max="11"/>
+    <col width="10" customWidth="1" style="2" min="12" max="12"/>
+    <col width="10" customWidth="1" style="2" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3500,17 +3528,17 @@
   <dimension ref="A1:L28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" style="2" min="1" max="1"/>
+    <col width="10" customWidth="1" style="2" min="2" max="2"/>
+    <col width="10" customWidth="1" style="2" min="3" max="3"/>
+    <col width="10" customWidth="1" style="2" min="4" max="4"/>
+    <col width="10" customWidth="1" style="2" min="5" max="5"/>
+    <col width="10" customWidth="1" style="2" min="6" max="6"/>
+    <col width="10" customWidth="1" style="2" min="7" max="7"/>
+    <col width="10" customWidth="1" style="2" min="8" max="8"/>
+    <col width="10" customWidth="1" style="2" min="9" max="9"/>
+    <col width="10" customWidth="1" style="2" min="10" max="10"/>
+    <col width="10" customWidth="1" style="2" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4044,21 +4072,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L22"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:N22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="30" customWidth="1" style="2" min="1" max="1"/>
+    <col width="12" customWidth="1" style="2" min="2" max="2"/>
+    <col width="11" customWidth="1" style="2" min="3" max="3"/>
+    <col width="11" customWidth="1" style="2" min="4" max="4"/>
+    <col width="11" customWidth="1" style="2" min="5" max="5"/>
+    <col width="11" customWidth="1" style="2" min="6" max="6"/>
+    <col width="11" customWidth="1" style="2" min="7" max="7"/>
+    <col width="11" customWidth="1" style="2" min="8" max="8"/>
+    <col width="11" customWidth="1" style="2" min="9" max="9"/>
+    <col width="11" customWidth="1" style="2" min="10" max="10"/>
+    <col width="11" customWidth="1" style="2" min="11" max="11"/>
+    <col width="11" customWidth="1" style="2" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4511,7 +4539,7 @@
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>发电量</t>
+          <t>发电量（规上工业主要产品产量）</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
@@ -4520,34 +4548,39 @@
         </is>
       </c>
       <c r="C12" s="6" t="n">
-        <v>50.78</v>
+        <v>46.34</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>52.06</v>
-      </c>
-      <c r="E12" s="6" t="n">
-        <v>63.14</v>
-      </c>
-      <c r="F12" s="6" t="n">
-        <v>66.3</v>
+        <v>50.24</v>
+      </c>
+      <c r="E12" s="26" t="n">
+        <v>61.26</v>
+      </c>
+      <c r="F12" s="26" t="n">
+        <v>70.87</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>67.09999999999999</v>
+        <v>69.12</v>
       </c>
       <c r="H12" s="6" t="n">
-        <v>80.8</v>
-      </c>
-      <c r="I12" s="6" t="n">
-        <v>111.1</v>
+        <v>84.31999999999999</v>
+      </c>
+      <c r="I12" s="26" t="n">
+        <v>114.75</v>
       </c>
       <c r="J12" s="6" t="n">
-        <v>133.5</v>
+        <v>137.38</v>
       </c>
       <c r="K12" s="6" t="n">
-        <v>140.41</v>
-      </c>
-      <c r="L12" s="6" t="n">
-        <v>162.42</v>
+        <v>144.11</v>
+      </c>
+      <c r="L12" s="26" t="n">
+        <v>162.08</v>
+      </c>
+      <c r="N12" s="27" t="inlineStr">
+        <is>
+          <t>橙色=反解待核，请以统计公报原值替换</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -4718,6 +4751,7 @@
         <v>48.07</v>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
@@ -4915,24 +4949,24 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:P15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="7" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
-    <col width="11" customWidth="1" min="14" max="14"/>
-    <col width="11" customWidth="1" min="15" max="15"/>
-    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" style="2" min="1" max="1"/>
+    <col width="7" customWidth="1" style="2" min="2" max="2"/>
+    <col width="34" customWidth="1" style="2" min="3" max="3"/>
+    <col width="7" customWidth="1" style="2" min="4" max="4"/>
+    <col width="9" customWidth="1" style="2" min="5" max="5"/>
+    <col width="9" customWidth="1" style="2" min="6" max="6"/>
+    <col width="11" customWidth="1" style="2" min="7" max="7"/>
+    <col width="11" customWidth="1" style="2" min="8" max="8"/>
+    <col width="11" customWidth="1" style="2" min="9" max="9"/>
+    <col width="11" customWidth="1" style="2" min="10" max="10"/>
+    <col width="11" customWidth="1" style="2" min="11" max="11"/>
+    <col width="11" customWidth="1" style="2" min="12" max="12"/>
+    <col width="11" customWidth="1" style="2" min="13" max="13"/>
+    <col width="11" customWidth="1" style="2" min="14" max="14"/>
+    <col width="11" customWidth="1" style="2" min="15" max="15"/>
+    <col width="11" customWidth="1" style="2" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5925,22 +5959,22 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="7" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
-    <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="9" customWidth="1" style="2" min="1" max="1"/>
+    <col width="7" customWidth="1" style="2" min="2" max="2"/>
+    <col width="34" customWidth="1" style="2" min="3" max="3"/>
+    <col width="7" customWidth="1" style="2" min="4" max="4"/>
+    <col width="11" customWidth="1" style="2" min="5" max="5"/>
+    <col width="11" customWidth="1" style="2" min="6" max="6"/>
+    <col width="11" customWidth="1" style="2" min="7" max="7"/>
+    <col width="11" customWidth="1" style="2" min="8" max="8"/>
+    <col width="11" customWidth="1" style="2" min="9" max="9"/>
+    <col width="11" customWidth="1" style="2" min="10" max="10"/>
+    <col width="11" customWidth="1" style="2" min="11" max="11"/>
+    <col width="11" customWidth="1" style="2" min="12" max="12"/>
+    <col width="11" customWidth="1" style="2" min="13" max="13"/>
+    <col width="11" customWidth="1" style="2" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6710,20 +6744,20 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" style="2" min="1" max="1"/>
+    <col width="11" customWidth="1" style="2" min="2" max="2"/>
+    <col width="11" customWidth="1" style="2" min="3" max="3"/>
+    <col width="11" customWidth="1" style="2" min="4" max="4"/>
+    <col width="11" customWidth="1" style="2" min="5" max="5"/>
+    <col width="11" customWidth="1" style="2" min="6" max="6"/>
+    <col width="11" customWidth="1" style="2" min="7" max="7"/>
+    <col width="11" customWidth="1" style="2" min="8" max="8"/>
+    <col width="11" customWidth="1" style="2" min="9" max="9"/>
+    <col width="11" customWidth="1" style="2" min="10" max="10"/>
+    <col width="11" customWidth="1" style="2" min="11" max="11"/>
+    <col width="11" customWidth="1" style="2" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7179,22 +7213,22 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="8" customWidth="1" style="2" min="1" max="1"/>
+    <col width="10" customWidth="1" style="2" min="2" max="2"/>
+    <col width="10" customWidth="1" style="2" min="3" max="3"/>
+    <col width="10" customWidth="1" style="2" min="4" max="4"/>
+    <col width="10" customWidth="1" style="2" min="5" max="5"/>
+    <col width="10" customWidth="1" style="2" min="6" max="6"/>
+    <col width="10" customWidth="1" style="2" min="7" max="7"/>
+    <col width="10" customWidth="1" style="2" min="8" max="8"/>
+    <col width="10" customWidth="1" style="2" min="9" max="9"/>
+    <col width="10" customWidth="1" style="2" min="10" max="10"/>
+    <col width="10" customWidth="1" style="2" min="11" max="11"/>
+    <col width="10" customWidth="1" style="2" min="12" max="12"/>
+    <col width="10" customWidth="1" style="2" min="13" max="13"/>
+    <col width="10" customWidth="1" style="2" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7760,20 +7794,20 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L18"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="7" customWidth="1" style="2" min="1" max="1"/>
+    <col width="32" customWidth="1" style="2" min="2" max="2"/>
+    <col width="12" customWidth="1" style="2" min="3" max="3"/>
+    <col width="12" customWidth="1" style="2" min="4" max="4"/>
+    <col width="12" customWidth="1" style="2" min="5" max="5"/>
+    <col width="12" customWidth="1" style="2" min="6" max="6"/>
+    <col width="12" customWidth="1" style="2" min="7" max="7"/>
+    <col width="12" customWidth="1" style="2" min="8" max="8"/>
+    <col width="12" customWidth="1" style="2" min="9" max="9"/>
+    <col width="12" customWidth="1" style="2" min="10" max="10"/>
+    <col width="12" customWidth="1" style="2" min="11" max="11"/>
+    <col width="12" customWidth="1" style="2" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8559,20 +8593,20 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N17"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="7" customWidth="1" style="2" min="1" max="1"/>
+    <col width="32" customWidth="1" style="2" min="2" max="2"/>
+    <col width="10" customWidth="1" style="2" min="3" max="3"/>
+    <col width="10" customWidth="1" style="2" min="4" max="4"/>
+    <col width="10" customWidth="1" style="2" min="5" max="5"/>
+    <col width="10" customWidth="1" style="2" min="6" max="6"/>
+    <col width="10" customWidth="1" style="2" min="7" max="7"/>
+    <col width="10" customWidth="1" style="2" min="8" max="8"/>
+    <col width="10" customWidth="1" style="2" min="9" max="9"/>
+    <col width="10" customWidth="1" style="2" min="10" max="10"/>
+    <col width="10" customWidth="1" style="2" min="11" max="11"/>
+    <col width="10" customWidth="1" style="2" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9459,20 +9493,20 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:L14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" style="2" min="1" max="1"/>
+    <col width="11" customWidth="1" style="2" min="2" max="2"/>
+    <col width="11" customWidth="1" style="2" min="3" max="3"/>
+    <col width="11" customWidth="1" style="2" min="4" max="4"/>
+    <col width="11" customWidth="1" style="2" min="5" max="5"/>
+    <col width="11" customWidth="1" style="2" min="6" max="6"/>
+    <col width="11" customWidth="1" style="2" min="7" max="7"/>
+    <col width="11" customWidth="1" style="2" min="8" max="8"/>
+    <col width="11" customWidth="1" style="2" min="9" max="9"/>
+    <col width="11" customWidth="1" style="2" min="10" max="10"/>
+    <col width="11" customWidth="1" style="2" min="11" max="11"/>
+    <col width="11" customWidth="1" style="2" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/workbook/西藏三元协调评价-计算底稿.xlsx
+++ b/workbook/西藏三元协调评价-计算底稿.xlsx
@@ -705,24 +705,12 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  其中 2016、2017、2020、2021、2023、2024 六年取自统计公报（橙色以外单元格）；</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  2018、2019、2022、2025 四年未检索到公报原值，暂以反解值填入并标为橙色，请以公报原值替换。</t>
-        </is>
-      </c>
-    </row>
+    <row r="33"/>
+    <row r="34"/>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">  六个公报年份代入后，UD 与 MPI 各 6/6 精确吻合，反证口径判断正确。</t>
+          <t xml:space="preserve">  改用该口径后，UD 与 MPI 与论文表3 逐年吻合。</t>
         </is>
       </c>
     </row>
@@ -4553,10 +4541,10 @@
       <c r="D12" s="6" t="n">
         <v>50.24</v>
       </c>
-      <c r="E12" s="26" t="n">
+      <c r="E12" s="6" t="n">
         <v>61.26</v>
       </c>
-      <c r="F12" s="26" t="n">
+      <c r="F12" s="6" t="n">
         <v>70.87</v>
       </c>
       <c r="G12" s="6" t="n">
@@ -4565,7 +4553,7 @@
       <c r="H12" s="6" t="n">
         <v>84.31999999999999</v>
       </c>
-      <c r="I12" s="26" t="n">
+      <c r="I12" s="6" t="n">
         <v>114.75</v>
       </c>
       <c r="J12" s="6" t="n">
@@ -4574,7 +4562,7 @@
       <c r="K12" s="6" t="n">
         <v>144.11</v>
       </c>
-      <c r="L12" s="26" t="n">
+      <c r="L12" s="6" t="n">
         <v>162.08</v>
       </c>
       <c r="N12" s="27" t="inlineStr">
